--- a/docs/oc-top-organismos/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos.xlsx
+++ b/docs/oc-top-organismos/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M47"/>
+  <dimension ref="A1:M63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>12947.67</v>
+        <v>12760.36</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>35483.34</v>
+        <v>34533.22</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>27119.25</v>
+        <v>26393.09</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>65683.16</v>
+        <v>63924.39</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>41430.64</v>
+        <v>40321.27</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>45917.56</v>
+        <v>46307.26</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>11556.92</v>
+        <v>11699.16</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>603876.53</v>
+        <v>611308.61</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>1213.96</v>
+        <v>1216.48</v>
       </c>
     </row>
     <row r="11">
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>61271.78</v>
+        <v>61853.9</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>4404-54-CM26</t>
+          <t>1176-39-CM26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1149,27 +1149,27 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>69.110.500-8</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MARPACIFICO SPA</t>
+          <t>INVERSIONES MTEA SPA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>77.173.533-9</t>
+          <t>76.366.361-2</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>55673.9</v>
+        <v>23758.03</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1176-39-CM26</t>
+          <t>162-194-CM26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1200,37 +1200,37 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>INVERSIONES MTEA SPA</t>
+          <t>Vivanet</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>76.366.361-2</t>
+          <t>76.018.259-1</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>23862.63</v>
+        <v>40387.43</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>162-194-CM26</t>
+          <t>930-85-CM26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1271,27 +1271,27 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Vivanet</t>
+          <t>JOSUE MANUEL</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>76.018.259-1</t>
+          <t>76.370.023-2</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1301,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>40831.61</v>
+        <v>1733.6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>930-85-CM26</t>
+          <t>299-85-CM26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1322,12 +1322,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1342,17 +1342,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>JOSUE MANUEL</t>
+          <t>Julio Saavedra</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>76.370.023-2</t>
+          <t>76.248.427-7</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>1737.89</v>
+        <v>53120.63</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>299-85-CM26</t>
+          <t>1434-94-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1393,27 +1393,27 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.104.022-9</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>Dirección General de Aeronáutica Civil</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Julio Saavedra</t>
+          <t>SMC</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>76.248.427-7</t>
+          <t>76.310.505-9</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>52860.96</v>
+        <v>403185.16</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1434-94-CM26</t>
+          <t>162-205-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1439,42 +1439,42 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>61.104.022-9</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dirección General de Aeronáutica Civil</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>SMC</t>
+          <t>Vivanet</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>76.310.505-9</t>
+          <t>76.018.259-1</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>401052.58</v>
+        <v>36943.03</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>162-205-CM26</t>
+          <t>1488-545-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1515,27 +1515,27 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>61.602.232-6</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Vivanet</t>
+          <t>TRANSERVI JL SPA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>76.018.259-1</t>
+          <t>77.063.031-2</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>36514.69</v>
+        <v>64684.58</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1488-545-CM26</t>
+          <t>1488-546-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>65088.11</v>
+        <v>27721.96</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1488-546-CM26</t>
+          <t>1488-639-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>27894.91</v>
+        <v>25279.97</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1488-639-CM26</t>
+          <t>997-77-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1688,37 +1688,37 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>61.602.232-6</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>TRANSERVI JL SPA</t>
+          <t>Sociedad Comercial de Transporte ICT Limitada</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>77.063.031-2</t>
+          <t>76.070.302-8</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>25437.68</v>
+        <v>33120.62</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>4451-352-CM26</t>
+          <t>1196-138-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1749,37 +1749,37 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>69.110.500-8</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>TRANSPORTES TOGUITA SPA</t>
+          <t>JOSUE MANUEL</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>77.549.439-5</t>
+          <t>76.370.023-2</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>64756.16</v>
+        <v>6911.17</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>4451-353-CM26</t>
+          <t>299-107-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1820,27 +1820,27 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>69.110.500-8</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA 9704 SPA</t>
+          <t>Julio Saavedra</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>77.171.057-3</t>
+          <t>76.248.427-7</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>8717.219999999999</v>
+        <v>1627.92</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1196-138-CM26</t>
+          <t>4215-17-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1881,27 +1881,27 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.104.022-9</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>Dirección General de Aeronáutica Civil</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>JOSUE MANUEL</t>
+          <t>PAULA ANDREA MERY NAVIA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>76.370.023-2</t>
+          <t>11.844.234-2</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>6929.5</v>
+        <v>75.89</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>997-77-CM26</t>
+          <t>934-82-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1942,27 +1942,27 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Sociedad Comercial de Transporte ICT Limitada</t>
+          <t>PAULA ANDREA MERY NAVIA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>76.070.302-8</t>
+          <t>11.844.234-2</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>33208.45</v>
+        <v>1626.3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>4404-131-CM26</t>
+          <t>934-85-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2003,27 +2003,27 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>69.110.500-8</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>MARPACIFICO SPA</t>
+          <t>ALEXANDER SEBASTIÁN BERG KROLL</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>77.173.533-9</t>
+          <t>8.148.859-2</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>8608.190000000001</v>
+        <v>31224.93</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>299-107-CM26</t>
+          <t>1062807-63-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2054,37 +2054,37 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>62.000.590-8</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION REGION ÑUBLE</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Julio Saavedra</t>
+          <t>DAVID ISAAC</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>76.248.427-7</t>
+          <t>76.820.816-6</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>1660.42</v>
+        <v>216839.78</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>4215-17-CM26</t>
+          <t>1057417-13722-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2125,27 +2125,27 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.104.022-9</t>
+          <t>61.607.301-K</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dirección General de Aeronáutica Civil</t>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>PAULA ANDREA MERY NAVIA</t>
+          <t>TRANSPORTES MONSALVE Y COMPAÑIA LIMITADA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>11.844.234-2</t>
+          <t>76.701.245-4</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>77.48999999999999</v>
+        <v>40430.05</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>934-82-CM26</t>
+          <t>934-86-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2201,12 +2201,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>PAULA ANDREA MERY NAVIA</t>
+          <t>TRANSPORTES RUTAMUSIC LIMITADA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>11.844.234-2</t>
+          <t>76.735.787-7</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>1660.42</v>
+        <v>6939.85</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>934-85-CM26</t>
+          <t>997-96-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2247,27 +2247,27 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>ALEXANDER SEBASTIÁN BERG KROLL</t>
+          <t>Sociedad Comercial de Transporte ICT Limitada</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>8.148.859-2</t>
+          <t>76.070.302-8</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>31880.12</v>
+        <v>10483.56</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1062807-63-CM26</t>
+          <t>934-88-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2308,27 +2308,27 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>62.000.590-8</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION REGION ÑUBLE</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>DAVID ISAAC</t>
+          <t>PAULA ANDREA MERY NAVIA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>76.820.816-6</t>
+          <t>11.844.234-2</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2338,13 +2338,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>221389.72</v>
+        <v>8605.07</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1057417-13722-CM26</t>
+          <t>1197-87-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2359,7 +2359,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2369,27 +2369,27 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.607.301-K</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>TRANSPORTES MONSALVE Y COMPAÑIA LIMITADA</t>
+          <t>Transporte Corporativo Infinity</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>76.701.245-4</t>
+          <t>76.207.531-8</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2399,13 +2399,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>40049.63</v>
+        <v>13993.69</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>934-86-CM26</t>
+          <t>1178-37-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2420,7 +2420,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2430,27 +2430,27 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>TRANSPORTES RUTAMUSIC LIMITADA</t>
+          <t>INVERSIONES MTEA SPA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>76.735.787-7</t>
+          <t>76.366.361-2</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2460,13 +2460,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>6874.55</v>
+        <v>46114.6</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>997-96-CM26</t>
+          <t>1196-151-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2491,27 +2491,27 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Sociedad Comercial de Transporte ICT Limitada</t>
+          <t>JOSUE MANUEL</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>76.070.302-8</t>
+          <t>76.370.023-2</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2521,13 +2521,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>10430.41</v>
+        <v>3767.53</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>934-88-CM26</t>
+          <t>5751-168-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2542,7 +2542,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2552,27 +2552,27 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.818.002-6</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION DE V</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>PAULA ANDREA MERY NAVIA</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>11.844.234-2</t>
+          <t>76.791.832-1</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2582,13 +2582,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>8571.700000000001</v>
+        <v>194424.62</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1197-87-CM26</t>
+          <t>1488-1054-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2603,37 +2603,37 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.602.232-6</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Transporte Corporativo Infinity</t>
+          <t>TRANSERVI JL SPA</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>76.207.531-8</t>
+          <t>77.063.031-2</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2643,13 +2643,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>13963.93</v>
+        <v>9732.040000000001</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1178-37-CM26</t>
+          <t>1523-1545-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2674,27 +2674,27 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.602.236-9</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>SERVICIO NACIONAL ARAUCANIA SUR HOSPITAL DR ABRAHAM GODOY PENA LAUTARO</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>INVERSIONES MTEA SPA</t>
+          <t>TRANSERVI JL SPA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>76.366.361-2</t>
+          <t>77.063.031-2</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -2704,13 +2704,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>46016.52</v>
+        <v>12330.98</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1196-151-CM26</t>
+          <t>2078-924-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2735,27 +2735,27 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>JOSUE MANUEL</t>
+          <t>CAROLYN MARLEN</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>76.370.023-2</t>
+          <t>76.905.851-6</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2765,13 +2765,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>3759.52</v>
+        <v>16061.33</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>5751-168-CM26</t>
+          <t>930-147-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2796,27 +2796,27 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>61.818.002-6</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION DE V</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>JOSUE MANUEL</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
+          <t>76.370.023-2</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2826,13 +2826,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>193131.89</v>
+        <v>5139.63</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1488-1054-CM26</t>
+          <t>1488-1053-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2847,7 +2847,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>9667.34</v>
+        <v>64308.63</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2078-924-CM26</t>
+          <t>934-94-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2908,7 +2908,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2918,27 +2918,27 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>CAROLYN MARLEN</t>
+          <t>PAULA ANDREA MERY NAVIA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>76.905.851-6</t>
+          <t>11.844.234-2</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2948,13 +2948,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>16112.23</v>
+        <v>18116.72</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>930-147-CM26</t>
+          <t>5602-184-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2979,27 +2979,27 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>JOSUE MANUEL</t>
+          <t>AUTORENTAS DEL PACIFICO SPA</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>76.370.023-2</t>
+          <t>83.547.100-4</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3009,13 +3009,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>5155.91</v>
+        <v>9303.450000000001</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1488-1053-CM26</t>
+          <t>299-124-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3030,37 +3030,37 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>61.602.232-6</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>TRANSERVI JL SPA</t>
+          <t>CAR PLACE SPA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>77.063.031-2</t>
+          <t>76.704.974-9</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3070,13 +3070,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>64448.86</v>
+        <v>10018.6</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>934-94-CM26</t>
+          <t>1057417-14563-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3101,27 +3101,27 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.607.301-K</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>PAULA ANDREA MERY NAVIA</t>
+          <t>TRANSPORTES MONSALVE Y COMPAÑIA LIMITADA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>11.844.234-2</t>
+          <t>76.701.245-4</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3131,13 +3131,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>18153.11</v>
+        <v>43703.37</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>5602-184-CM26</t>
+          <t>932-136-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3147,12 +3147,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3162,27 +3162,27 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Región del Libertador General Bernardo O´Higgins</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>AUTORENTAS DEL PACIFICO SPA</t>
+          <t>Sociedad de Transporte Jiménez Hermanos Ltda.</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>83.547.100-4</t>
+          <t>76.036.979-9</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3192,13 +3192,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>9357.610000000001</v>
+        <v>2350.12</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>299-124-CM26</t>
+          <t>934-114-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3233,17 +3233,17 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t xml:space="preserve">Región de los Lagos </t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>CAR PLACE SPA</t>
+          <t>PAULA ANDREA MERY NAVIA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>76.704.974-9</t>
+          <t>11.844.234-2</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3253,13 +3253,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>10182.93</v>
+        <v>2594.9</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1057417-14563-CM26</t>
+          <t>1178-45-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3284,27 +3284,27 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>61.607.301-K</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t xml:space="preserve">Región de Coquimbo </t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>TRANSPORTES MONSALVE Y COMPAÑIA LIMITADA</t>
+          <t>INVERSIONES MTEA SPA</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>76.701.245-4</t>
+          <t>76.366.361-2</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -3314,7 +3314,983 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>43412.78</v>
+        <v>183957.01</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>1488-904-CM26</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>61.602.232-6</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de la Araucanía </t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>TRANSERVI JL SPA</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>77.063.031-2</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="n">
+        <v>83035.34</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>1488-903-CM26</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>61.602.232-6</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de la Araucanía </t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>TRANSERVI JL SPA</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>77.063.031-2</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="n">
+        <v>208859.42</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>932-138-CM26</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>61.107.000-4</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Región del Libertador General Bernardo O´Higgins</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Sociedad de Transporte Jiménez Hermanos Ltda.</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>76.036.979-9</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="n">
+        <v>21934.59</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>1057417-14549-CM26</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>61.607.301-K</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Biobío </t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Transportes Luis Rifo y compañia limitada</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>76.114.087-6</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="n">
+        <v>37143.95</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>1057417-14604-CM26</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>61.607.301-K</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Biobío </t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Transportes Luis Rifo y compañia limitada</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>76.114.087-6</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="n">
+        <v>3535.96</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>1197-97-CM26</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>61.107.000-4</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Transporte Corporativo Infinity</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>76.207.531-8</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="n">
+        <v>15278.84</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>934-131-CM26</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>61.107.000-4</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>PAULA ANDREA MERY NAVIA</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>11.844.234-2</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="n">
+        <v>2960.53</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>1197-99-CM26</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>61.107.000-4</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Atacama </t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>CAR PLACE SPA</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>76.704.974-9</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="n">
+        <v>27355.86</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>1523-1816-CM26</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>61.602.236-9</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL ARAUCANIA SUR HOSPITAL DR ABRAHAM GODOY PENA LAUTARO</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de la Araucanía </t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>LUIS ALBERTO PAILLAMILLA OÑATE</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>16.995.419-4</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="n">
+        <v>249028.09</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>934-134-CM26</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>61.107.000-4</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>PAULA ANDREA MERY NAVIA</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>11.844.234-2</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="n">
+        <v>3942.4</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>934-136-CM26</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>61.107.000-4</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de los Lagos </t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>TURISMO Y EXCURSIONES PATAGON AUSTRAL SPA</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>77.659.446-6</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="n">
+        <v>878.41</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>1198-203-CM26</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>61.107.000-4</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Felipe </t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>76.834.013-7</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="n">
+        <v>5193.3</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>1057417-15339-CM26</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>61.607.301-K</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región del Biobío </t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>TURISMO AYEKANTUN LIMITADA</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>76.470.279-4</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="n">
+        <v>42076.74</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>932-152-CM26</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>61.107.000-4</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Región del Libertador General Bernardo O´Higgins</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Sociedad de Transporte Jiménez Hermanos Ltda.</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>76.036.979-9</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="n">
+        <v>17149.02</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>932-155-CM26</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>61.107.000-4</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Región del Libertador General Bernardo O´Higgins</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>CAR PLACE SPA</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>76.704.974-9</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="n">
+        <v>35882.19</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>1197-107-CM26</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>61.107.000-4</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Atacama </t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Felipe </t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>76.834.013-7</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="n">
+        <v>1452.68</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-top-organismos/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos.xlsx
+++ b/docs/oc-top-organismos/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="transporte-priva top org" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="transporte-priva top org" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M63"/>
+  <dimension ref="A1:M64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1673,7 +1673,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>997-77-CM26</t>
+          <t>1392-57-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1698,27 +1698,27 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.104.000-8</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Sociedad Comercial de Transporte ICT Limitada</t>
+          <t>AUTOMOTRIZ R y R LIMITADA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>76.070.302-8</t>
+          <t>77.951.690-3</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>33120.62</v>
+        <v>12017.6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1196-138-CM26</t>
+          <t>997-77-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1759,27 +1759,27 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>JOSUE MANUEL</t>
+          <t>Sociedad Comercial de Transporte ICT Limitada</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>76.370.023-2</t>
+          <t>76.070.302-8</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>6911.17</v>
+        <v>33120.62</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>299-107-CM26</t>
+          <t>1196-138-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1830,17 +1830,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Julio Saavedra</t>
+          <t>JOSUE MANUEL</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>76.248.427-7</t>
+          <t>76.370.023-2</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>1627.92</v>
+        <v>6911.17</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>4215-17-CM26</t>
+          <t>299-107-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1871,37 +1871,37 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>61.104.022-9</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dirección General de Aeronáutica Civil</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>PAULA ANDREA MERY NAVIA</t>
+          <t>Julio Saavedra</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>11.844.234-2</t>
+          <t>76.248.427-7</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>75.89</v>
+        <v>1627.92</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>934-82-CM26</t>
+          <t>4215-17-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.104.022-9</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>Dirección General de Aeronáutica Civil</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>1626.3</v>
+        <v>75.89</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>934-85-CM26</t>
+          <t>934-82-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>ALEXANDER SEBASTIÁN BERG KROLL</t>
+          <t>PAULA ANDREA MERY NAVIA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>8.148.859-2</t>
+          <t>11.844.234-2</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>31224.93</v>
+        <v>1626.3</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1062807-63-CM26</t>
+          <t>934-85-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2064,27 +2064,27 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>62.000.590-8</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION REGION ÑUBLE</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>DAVID ISAAC</t>
+          <t>ALEXANDER SEBASTIÁN BERG KROLL</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>76.820.816-6</t>
+          <t>8.148.859-2</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>216839.78</v>
+        <v>31224.93</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1057417-13722-CM26</t>
+          <t>1062807-63-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2125,27 +2125,27 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.607.301-K</t>
+          <t>62.000.590-8</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION REGION ÑUBLE</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>TRANSPORTES MONSALVE Y COMPAÑIA LIMITADA</t>
+          <t>DAVID ISAAC</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>76.701.245-4</t>
+          <t>76.820.816-6</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>40430.05</v>
+        <v>216839.78</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>934-86-CM26</t>
+          <t>1057417-13722-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2186,27 +2186,27 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.607.301-K</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>TRANSPORTES RUTAMUSIC LIMITADA</t>
+          <t>TRANSPORTES MONSALVE Y COMPAÑIA LIMITADA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>76.735.787-7</t>
+          <t>76.701.245-4</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>6939.85</v>
+        <v>40430.05</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>997-96-CM26</t>
+          <t>934-86-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2247,27 +2247,27 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Sociedad Comercial de Transporte ICT Limitada</t>
+          <t>TRANSPORTES RUTAMUSIC LIMITADA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>76.070.302-8</t>
+          <t>76.735.787-7</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>10483.56</v>
+        <v>6939.85</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>934-88-CM26</t>
+          <t>997-96-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2308,27 +2308,27 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>PAULA ANDREA MERY NAVIA</t>
+          <t>Sociedad Comercial de Transporte ICT Limitada</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>11.844.234-2</t>
+          <t>76.070.302-8</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2338,13 +2338,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>8605.07</v>
+        <v>10483.56</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1197-87-CM26</t>
+          <t>934-88-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2359,7 +2359,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2379,17 +2379,17 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Transporte Corporativo Infinity</t>
+          <t>PAULA ANDREA MERY NAVIA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>76.207.531-8</t>
+          <t>11.844.234-2</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2399,13 +2399,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>13993.69</v>
+        <v>8605.07</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1178-37-CM26</t>
+          <t>1197-87-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2430,27 +2430,27 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>INVERSIONES MTEA SPA</t>
+          <t>Transporte Corporativo Infinity</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>76.366.361-2</t>
+          <t>76.207.531-8</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2460,13 +2460,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>46114.6</v>
+        <v>13993.69</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1196-151-CM26</t>
+          <t>1178-37-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2491,27 +2491,27 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>JOSUE MANUEL</t>
+          <t>INVERSIONES MTEA SPA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>76.370.023-2</t>
+          <t>76.366.361-2</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2521,13 +2521,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>3767.53</v>
+        <v>46114.6</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>5751-168-CM26</t>
+          <t>1196-151-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2542,7 +2542,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2552,27 +2552,27 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>61.818.002-6</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION DE V</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>JOSUE MANUEL</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
+          <t>76.370.023-2</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2582,13 +2582,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>194424.62</v>
+        <v>3767.53</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1488-1054-CM26</t>
+          <t>5751-168-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2608,32 +2608,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>61.602.232-6</t>
+          <t>61.818.002-6</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION DE V</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>TRANSERVI JL SPA</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>77.063.031-2</t>
+          <t>76.791.832-1</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2643,13 +2643,13 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>9732.040000000001</v>
+        <v>194424.62</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1523-1545-CM26</t>
+          <t>1488-1054-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2664,22 +2664,22 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>61.602.236-9</t>
+          <t>61.602.232-6</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL ARAUCANIA SUR HOSPITAL DR ABRAHAM GODOY PENA LAUTARO</t>
+          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2704,13 +2704,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>12330.98</v>
+        <v>9732.040000000001</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2078-924-CM26</t>
+          <t>1523-1545-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2735,27 +2735,27 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>61.602.236-9</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>SERVICIO NACIONAL ARAUCANIA SUR HOSPITAL DR ABRAHAM GODOY PENA LAUTARO</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>CAROLYN MARLEN</t>
+          <t>TRANSERVI JL SPA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>76.905.851-6</t>
+          <t>77.063.031-2</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2765,13 +2765,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>16061.33</v>
+        <v>12330.98</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>930-147-CM26</t>
+          <t>2078-924-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2796,27 +2796,27 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>JOSUE MANUEL</t>
+          <t>CAROLYN MARLEN</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>76.370.023-2</t>
+          <t>76.905.851-6</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2826,13 +2826,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>5139.63</v>
+        <v>16061.33</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1488-1053-CM26</t>
+          <t>930-147-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2847,37 +2847,37 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>61.602.232-6</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>TRANSERVI JL SPA</t>
+          <t>JOSUE MANUEL</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>77.063.031-2</t>
+          <t>76.370.023-2</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>64308.63</v>
+        <v>5139.63</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>934-94-CM26</t>
+          <t>1488-1053-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2908,37 +2908,37 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.602.232-6</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>PAULA ANDREA MERY NAVIA</t>
+          <t>TRANSERVI JL SPA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>11.844.234-2</t>
+          <t>77.063.031-2</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2948,13 +2948,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>18116.72</v>
+        <v>64308.63</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>5602-184-CM26</t>
+          <t>934-94-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2979,27 +2979,27 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>AUTORENTAS DEL PACIFICO SPA</t>
+          <t>PAULA ANDREA MERY NAVIA</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>83.547.100-4</t>
+          <t>11.844.234-2</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3009,13 +3009,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>9303.450000000001</v>
+        <v>18116.72</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>299-124-CM26</t>
+          <t>5602-184-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3040,27 +3040,27 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>CAR PLACE SPA</t>
+          <t>AUTORENTAS DEL PACIFICO SPA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>76.704.974-9</t>
+          <t>83.547.100-4</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3070,13 +3070,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>10018.6</v>
+        <v>9303.450000000001</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1057417-14563-CM26</t>
+          <t>299-124-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3101,27 +3101,27 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>61.607.301-K</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>TRANSPORTES MONSALVE Y COMPAÑIA LIMITADA</t>
+          <t>CAR PLACE SPA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>76.701.245-4</t>
+          <t>76.704.974-9</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3131,13 +3131,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>43703.37</v>
+        <v>10018.6</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>932-136-CM26</t>
+          <t>1057417-14563-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3147,12 +3147,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3162,27 +3162,27 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.607.301-K</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Sociedad de Transporte Jiménez Hermanos Ltda.</t>
+          <t>TRANSPORTES MONSALVE Y COMPAÑIA LIMITADA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>76.036.979-9</t>
+          <t>76.701.245-4</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3192,13 +3192,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>2350.12</v>
+        <v>43703.37</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>934-114-CM26</t>
+          <t>932-136-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3233,17 +3233,17 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>PAULA ANDREA MERY NAVIA</t>
+          <t>Sociedad de Transporte Jiménez Hermanos Ltda.</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>11.844.234-2</t>
+          <t>76.036.979-9</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3253,13 +3253,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>2594.9</v>
+        <v>2350.12</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1178-45-CM26</t>
+          <t>934-114-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3284,27 +3284,27 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>INVERSIONES MTEA SPA</t>
+          <t>PAULA ANDREA MERY NAVIA</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>76.366.361-2</t>
+          <t>11.844.234-2</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>183957.01</v>
+        <v>2594.9</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1488-904-CM26</t>
+          <t>1178-45-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3340,32 +3340,32 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>61.602.232-6</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>TRANSERVI JL SPA</t>
+          <t>INVERSIONES MTEA SPA</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>77.063.031-2</t>
+          <t>76.366.361-2</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3375,13 +3375,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>83035.34</v>
+        <v>183957.01</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1488-903-CM26</t>
+          <t>1488-904-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3436,13 +3436,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>208859.42</v>
+        <v>83035.34</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>932-138-CM26</t>
+          <t>1488-903-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3467,27 +3467,27 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.602.232-6</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Sociedad de Transporte Jiménez Hermanos Ltda.</t>
+          <t>TRANSERVI JL SPA</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>76.036.979-9</t>
+          <t>77.063.031-2</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3497,13 +3497,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>21934.59</v>
+        <v>208859.42</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1057417-14549-CM26</t>
+          <t>932-138-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3518,37 +3518,37 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>61.607.301-K</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Transportes Luis Rifo y compañia limitada</t>
+          <t>Sociedad de Transporte Jiménez Hermanos Ltda.</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>76.114.087-6</t>
+          <t>76.036.979-9</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -3558,13 +3558,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>37143.95</v>
+        <v>21934.59</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1057417-14604-CM26</t>
+          <t>1057417-14549-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3619,13 +3619,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>3535.96</v>
+        <v>37143.95</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1197-97-CM26</t>
+          <t>1057417-14604-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3645,32 +3645,32 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.607.301-K</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Transporte Corporativo Infinity</t>
+          <t>Transportes Luis Rifo y compañia limitada</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>76.207.531-8</t>
+          <t>76.114.087-6</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -3680,13 +3680,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>15278.84</v>
+        <v>3535.96</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>934-131-CM26</t>
+          <t>1197-97-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3721,17 +3721,17 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>PAULA ANDREA MERY NAVIA</t>
+          <t>Transporte Corporativo Infinity</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>11.844.234-2</t>
+          <t>76.207.531-8</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -3741,13 +3741,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>2960.53</v>
+        <v>15278.84</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1197-99-CM26</t>
+          <t>934-131-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -3782,17 +3782,17 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>CAR PLACE SPA</t>
+          <t>PAULA ANDREA MERY NAVIA</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>76.704.974-9</t>
+          <t>11.844.234-2</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3802,13 +3802,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>27355.86</v>
+        <v>2960.53</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1523-1816-CM26</t>
+          <t>1197-99-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3833,27 +3833,27 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>61.602.236-9</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL ARAUCANIA SUR HOSPITAL DR ABRAHAM GODOY PENA LAUTARO</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>LUIS ALBERTO PAILLAMILLA OÑATE</t>
+          <t>CAR PLACE SPA</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>16.995.419-4</t>
+          <t>76.704.974-9</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -3863,13 +3863,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>249028.09</v>
+        <v>27355.86</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>934-134-CM26</t>
+          <t>1523-1816-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3894,27 +3894,27 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.602.236-9</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>SERVICIO NACIONAL ARAUCANIA SUR HOSPITAL DR ABRAHAM GODOY PENA LAUTARO</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>PAULA ANDREA MERY NAVIA</t>
+          <t>LUIS ALBERTO PAILLAMILLA OÑATE</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>11.844.234-2</t>
+          <t>16.995.419-4</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -3924,13 +3924,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>3942.4</v>
+        <v>249028.09</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>934-136-CM26</t>
+          <t>934-134-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3945,7 +3945,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3965,17 +3965,17 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>TURISMO Y EXCURSIONES PATAGON AUSTRAL SPA</t>
+          <t>PAULA ANDREA MERY NAVIA</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>77.659.446-6</t>
+          <t>11.844.234-2</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -3985,13 +3985,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>878.41</v>
+        <v>3942.4</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1198-203-CM26</t>
+          <t>934-136-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4026,17 +4026,17 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Felipe </t>
+          <t>TURISMO Y EXCURSIONES PATAGON AUSTRAL SPA</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>76.834.013-7</t>
+          <t>77.659.446-6</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -4046,13 +4046,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>5193.3</v>
+        <v>878.41</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1057417-15339-CM26</t>
+          <t>1198-203-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4077,27 +4077,27 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>61.607.301-K</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>TURISMO AYEKANTUN LIMITADA</t>
+          <t xml:space="preserve">Felipe </t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>76.470.279-4</t>
+          <t>76.834.013-7</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4107,13 +4107,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>42076.74</v>
+        <v>5193.3</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>932-152-CM26</t>
+          <t>1057417-15339-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4138,27 +4138,27 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.607.301-K</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Sociedad de Transporte Jiménez Hermanos Ltda.</t>
+          <t>TURISMO AYEKANTUN LIMITADA</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>76.036.979-9</t>
+          <t>76.470.279-4</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -4168,13 +4168,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>17149.02</v>
+        <v>42076.74</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>932-155-CM26</t>
+          <t>932-152-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4189,7 +4189,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4209,17 +4209,17 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>CAR PLACE SPA</t>
+          <t>Sociedad de Transporte Jiménez Hermanos Ltda.</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>76.704.974-9</t>
+          <t>76.036.979-9</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>35882.19</v>
+        <v>17149.02</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1197-107-CM26</t>
+          <t>932-155-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4270,17 +4270,17 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Felipe </t>
+          <t>CAR PLACE SPA</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>76.834.013-7</t>
+          <t>76.704.974-9</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -4290,6 +4290,67 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
+        <v>35882.19</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>1197-107-CM26</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>61.107.000-4</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Felipe </t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>76.834.013-7</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="n">
         <v>1452.68</v>
       </c>
     </row>

--- a/docs/oc-top-organismos/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos.xlsx
+++ b/docs/oc-top-organismos/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M64"/>
+  <dimension ref="A1:M80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Vivanet</t>
+          <t>VIVANET</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dirección General de Aeronáutica Civil</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Vivanet</t>
+          <t>VIVANET</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1490,7 +1490,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1488-545-CM26</t>
+          <t>1488-546-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>64684.58</v>
+        <v>27721.96</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1488-546-CM26</t>
+          <t>1488-639-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>27721.96</v>
+        <v>25279.97</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1488-639-CM26</t>
+          <t>1488-545-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>25279.97</v>
+        <v>64684.58</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1392-57-CM26</t>
+          <t>934-81-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1698,27 +1698,27 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>61.104.000-8</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ R y R LIMITADA</t>
+          <t>PAULA ANDREA MERY NAVIA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>77.951.690-3</t>
+          <t>11.844.234-2</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>12017.6</v>
+        <v>1548.17</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>997-77-CM26</t>
+          <t>1392-57-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1759,27 +1759,27 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.104.000-8</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Sociedad Comercial de Transporte ICT Limitada</t>
+          <t>AUTOMOTRIZ R Y R LIMITADA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>76.070.302-8</t>
+          <t>77.951.690-3</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>33120.62</v>
+        <v>12017.6</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1196-138-CM26</t>
+          <t>997-77-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1820,27 +1820,27 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>JOSUE MANUEL</t>
+          <t>Sociedad Comercial de Transporte ICT Limitada</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>76.370.023-2</t>
+          <t>76.070.302-8</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>6911.17</v>
+        <v>33120.62</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>299-107-CM26</t>
+          <t>1196-138-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1871,12 +1871,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1891,17 +1891,17 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Julio Saavedra</t>
+          <t>JOSUE MANUEL</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>76.248.427-7</t>
+          <t>76.370.023-2</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>1627.92</v>
+        <v>6911.17</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>4215-17-CM26</t>
+          <t>299-107-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1932,37 +1932,37 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>61.104.022-9</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dirección General de Aeronáutica Civil</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>PAULA ANDREA MERY NAVIA</t>
+          <t>Julio Saavedra</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>11.844.234-2</t>
+          <t>76.248.427-7</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>75.89</v>
+        <v>1627.92</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>934-82-CM26</t>
+          <t>1062807-63-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2003,27 +2003,27 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>62.000.590-8</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION REGION ÑUBLE</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>PAULA ANDREA MERY NAVIA</t>
+          <t>David Isaac</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>11.844.234-2</t>
+          <t>76.820.816-6</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>1626.3</v>
+        <v>216839.78</v>
       </c>
     </row>
     <row r="27">
@@ -2100,7 +2100,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1062807-63-CM26</t>
+          <t>4215-17-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2125,27 +2125,27 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>62.000.590-8</t>
+          <t>61.104.022-9</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION REGION ÑUBLE</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>DAVID ISAAC</t>
+          <t>PAULA ANDREA MERY NAVIA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>76.820.816-6</t>
+          <t>11.844.234-2</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2155,13 +2155,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>216839.78</v>
+        <v>75.89</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1057417-13722-CM26</t>
+          <t>934-82-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2171,42 +2171,42 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>61.607.301-K</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>TRANSPORTES MONSALVE Y COMPAÑIA LIMITADA</t>
+          <t>PAULA ANDREA MERY NAVIA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>76.701.245-4</t>
+          <t>11.844.234-2</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2216,13 +2216,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>40430.05</v>
+        <v>1626.3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>934-86-CM26</t>
+          <t>1057417-13722-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2242,32 +2242,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.607.301-K</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>TRANSPORTES RUTAMUSIC LIMITADA</t>
+          <t>TRANSPORTES MONSALVE Y COMPAÑIA LIMITADA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>76.735.787-7</t>
+          <t>76.701.245-4</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>6939.85</v>
+        <v>40430.05</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>997-96-CM26</t>
+          <t>934-86-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2308,27 +2308,27 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Sociedad Comercial de Transporte ICT Limitada</t>
+          <t>TRANSPORTES RUTAMUSIC LIMITADA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>76.070.302-8</t>
+          <t>76.735.787-7</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
@@ -2338,13 +2338,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>10483.56</v>
+        <v>6939.85</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>934-88-CM26</t>
+          <t>997-96-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2359,7 +2359,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2369,27 +2369,27 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>PAULA ANDREA MERY NAVIA</t>
+          <t>Sociedad Comercial de Transporte ICT Limitada</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>11.844.234-2</t>
+          <t>76.070.302-8</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
@@ -2399,13 +2399,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>8605.07</v>
+        <v>10483.56</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1197-87-CM26</t>
+          <t>934-88-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2420,7 +2420,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2440,17 +2440,17 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Transporte Corporativo Infinity</t>
+          <t>PAULA ANDREA MERY NAVIA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>76.207.531-8</t>
+          <t>11.844.234-2</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2460,13 +2460,13 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>13993.69</v>
+        <v>8605.07</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1178-37-CM26</t>
+          <t>1196-151-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2491,27 +2491,27 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>INVERSIONES MTEA SPA</t>
+          <t>JOSUE MANUEL</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>76.366.361-2</t>
+          <t>76.370.023-2</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2521,13 +2521,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>46114.6</v>
+        <v>3767.53</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1196-151-CM26</t>
+          <t>1178-37-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2552,27 +2552,27 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>JOSUE MANUEL</t>
+          <t>INVERSIONES MTEA SPA</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>76.370.023-2</t>
+          <t>76.366.361-2</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2582,13 +2582,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>3767.53</v>
+        <v>46114.6</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>5751-168-CM26</t>
+          <t>1197-87-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2613,27 +2613,27 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>61.818.002-6</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION DE V</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>Transporte Corporativo Infinity</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
+          <t>76.207.531-8</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>194424.62</v>
+        <v>13993.69</v>
       </c>
     </row>
     <row r="37">
@@ -2710,7 +2710,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1523-1545-CM26</t>
+          <t>5751-168-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2735,27 +2735,27 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>61.602.236-9</t>
+          <t>61.818.002-6</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL ARAUCANIA SUR HOSPITAL DR ABRAHAM GODOY PENA LAUTARO</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION DE V</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>TRANSERVI JL SPA</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>77.063.031-2</t>
+          <t>76.791.832-1</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2765,13 +2765,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>12330.98</v>
+        <v>194424.62</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2078-924-CM26</t>
+          <t>1523-1545-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2796,27 +2796,27 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>61.602.236-9</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>SERVICIO NACIONAL ARAUCANIA SUR HOSPITAL DR ABRAHAM GODOY PENA LAUTARO</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>CAROLYN MARLEN</t>
+          <t>TRANSERVI JL SPA</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>76.905.851-6</t>
+          <t>77.063.031-2</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>16061.33</v>
+        <v>12330.98</v>
       </c>
     </row>
     <row r="40">
@@ -2893,7 +2893,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1488-1053-CM26</t>
+          <t>2078-924-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2908,37 +2908,37 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>61.602.232-6</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>TRANSERVI JL SPA</t>
+          <t>CAROLYN MARLEN</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>77.063.031-2</t>
+          <t>76.905.851-6</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -2948,13 +2948,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>64308.63</v>
+        <v>16061.33</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>934-94-CM26</t>
+          <t>1488-1053-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2969,37 +2969,37 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.602.232-6</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>PAULA ANDREA MERY NAVIA</t>
+          <t>TRANSERVI JL SPA</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>11.844.234-2</t>
+          <t>77.063.031-2</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3009,13 +3009,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>18116.72</v>
+        <v>64308.63</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>5602-184-CM26</t>
+          <t>934-94-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3040,27 +3040,27 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>AUTORENTAS DEL PACIFICO SPA</t>
+          <t>PAULA ANDREA MERY NAVIA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>83.547.100-4</t>
+          <t>11.844.234-2</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3070,13 +3070,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>9303.450000000001</v>
+        <v>18116.72</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>299-124-CM26</t>
+          <t>5602-184-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3101,27 +3101,27 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>CAR PLACE SPA</t>
+          <t>AUTORENTAS DEL PACIFICO SPA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>76.704.974-9</t>
+          <t>83.547.100-4</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3131,13 +3131,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>10018.6</v>
+        <v>9303.450000000001</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1057417-14563-CM26</t>
+          <t>299-124-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3162,27 +3162,27 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>61.607.301-K</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>TRANSPORTES MONSALVE Y COMPAÑIA LIMITADA</t>
+          <t>CAR PLACE SPA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>76.701.245-4</t>
+          <t>76.704.974-9</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3192,13 +3192,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>43703.37</v>
+        <v>10018.6</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>932-136-CM26</t>
+          <t>1057417-14563-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3223,27 +3223,27 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.607.301-K</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Sociedad de Transporte Jiménez Hermanos Ltda.</t>
+          <t>TRANSPORTES MONSALVE Y COMPAÑIA LIMITADA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>76.036.979-9</t>
+          <t>76.701.245-4</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>2350.12</v>
+        <v>43703.37</v>
       </c>
     </row>
     <row r="47">
@@ -3381,7 +3381,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1488-904-CM26</t>
+          <t>932-136-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>61.602.232-6</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>TRANSERVI JL SPA</t>
+          <t>Sociedad de Transporte Jiménez Hermanos Ltda.</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>77.063.031-2</t>
+          <t>76.036.979-9</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>83035.34</v>
+        <v>2350.12</v>
       </c>
     </row>
     <row r="50">
@@ -3503,7 +3503,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>932-138-CM26</t>
+          <t>1488-904-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3528,27 +3528,27 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.602.232-6</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Sociedad de Transporte Jiménez Hermanos Ltda.</t>
+          <t>TRANSERVI JL SPA</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>76.036.979-9</t>
+          <t>77.063.031-2</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -3558,13 +3558,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>21934.59</v>
+        <v>83035.34</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1057417-14549-CM26</t>
+          <t>932-138-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3579,37 +3579,37 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>61.607.301-K</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Transportes Luis Rifo y compañia limitada</t>
+          <t>Sociedad de Transporte Jiménez Hermanos Ltda.</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>76.114.087-6</t>
+          <t>76.036.979-9</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -3619,13 +3619,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>37143.95</v>
+        <v>21934.59</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1057417-14604-CM26</t>
+          <t>1057417-14549-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3680,13 +3680,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>3535.96</v>
+        <v>37143.95</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1197-97-CM26</t>
+          <t>1057417-14604-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3706,32 +3706,32 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.607.301-K</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Transporte Corporativo Infinity</t>
+          <t>Transportes Luis Rifo y compañia limitada</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>76.207.531-8</t>
+          <t>76.114.087-6</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -3741,13 +3741,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>15278.84</v>
+        <v>3535.96</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>934-131-CM26</t>
+          <t>1197-97-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3782,17 +3782,17 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>PAULA ANDREA MERY NAVIA</t>
+          <t>Transporte Corporativo Infinity</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>11.844.234-2</t>
+          <t>76.207.531-8</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3802,13 +3802,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>2960.53</v>
+        <v>15278.84</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1197-99-CM26</t>
+          <t>934-131-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3843,17 +3843,17 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>CAR PLACE SPA</t>
+          <t>PAULA ANDREA MERY NAVIA</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>76.704.974-9</t>
+          <t>11.844.234-2</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>27355.86</v>
+        <v>2960.53</v>
       </c>
     </row>
     <row r="57">
@@ -3930,7 +3930,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>934-134-CM26</t>
+          <t>1197-99-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3965,17 +3965,17 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>PAULA ANDREA MERY NAVIA</t>
+          <t>CAR PLACE SPA</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>11.844.234-2</t>
+          <t>76.704.974-9</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -3985,13 +3985,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>3942.4</v>
+        <v>27355.86</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>934-136-CM26</t>
+          <t>934-134-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4031,12 +4031,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>TURISMO Y EXCURSIONES PATAGON AUSTRAL SPA</t>
+          <t>PAULA ANDREA MERY NAVIA</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>77.659.446-6</t>
+          <t>11.844.234-2</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -4046,13 +4046,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>878.41</v>
+        <v>3942.4</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1198-203-CM26</t>
+          <t>934-136-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -4087,17 +4087,17 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Felipe </t>
+          <t>TURISMO Y EXCURSIONES PATAGON AUSTRAL SPA</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>76.834.013-7</t>
+          <t>77.659.446-6</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4107,13 +4107,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>5193.3</v>
+        <v>878.41</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1057417-15339-CM26</t>
+          <t>1198-203-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4138,27 +4138,27 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>61.607.301-K</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>TURISMO AYEKANTUN LIMITADA</t>
+          <t xml:space="preserve">Felipe </t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>76.470.279-4</t>
+          <t>76.834.013-7</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -4168,13 +4168,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>42076.74</v>
+        <v>5193.3</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>932-152-CM26</t>
+          <t>1057417-15339-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4189,7 +4189,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4199,27 +4199,27 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.607.301-K</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Sociedad de Transporte Jiménez Hermanos Ltda.</t>
+          <t>TURISMO AYEKANTUN LIMITADA</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>76.036.979-9</t>
+          <t>76.470.279-4</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>17149.02</v>
+        <v>42076.74</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>932-155-CM26</t>
+          <t>932-152-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4275,12 +4275,12 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>CAR PLACE SPA</t>
+          <t>Sociedad de Transporte Jiménez Hermanos Ltda.</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>76.704.974-9</t>
+          <t>76.036.979-9</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -4290,13 +4290,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>35882.19</v>
+        <v>17149.02</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1197-107-CM26</t>
+          <t>932-155-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4331,17 +4331,17 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Felipe </t>
+          <t>CAR PLACE SPA</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>76.834.013-7</t>
+          <t>76.704.974-9</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
@@ -4351,7 +4351,983 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
+        <v>35882.19</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>1197-107-CM26</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>61.107.000-4</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Felipe </t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>76.834.013-7</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="n">
         <v>1452.68</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>1488-1234-CM26</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>61.602.232-6</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>TRANSERVI JL SPA</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>77.063.031-2</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="n">
+        <v>46989.46</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>1199-213-CM26</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>61.107.000-4</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>BUSES VILLAR</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>76.465.610-5</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="n">
+        <v>38554.16</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>299-168-CM26</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>61.107.000-4</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Los Ríos</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>CAR PLACE SPA</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>76.704.974-9</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="n">
+        <v>77200.13</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>933-88-CM26</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>61.107.000-4</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>TURISMO AYEKANTUN LIMITADA</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>76.470.279-4</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="n">
+        <v>3841.35</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>931-165-CM26</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>61.107.000-4</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>JOSUE MANUEL</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>76.370.023-2</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="n">
+        <v>20647.27</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>933-70-CM26</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>61.107.000-4</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>TURISMO AYEKANTUN LIMITADA</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>76.470.279-4</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="n">
+        <v>85024.07000000001</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2123-317-CM26</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>61.601.000-K</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Empresa de Transportes Pablo Jaramillo Benavente E</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>76.076.244-k</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="n">
+        <v>10096.61</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>931-167-CM26</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>61.107.000-4</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>CAR PLACE SPA</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>76.704.974-9</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="n">
+        <v>9912.15</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>1197-122-CM26</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>61.107.000-4</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Transporte Corporativo Infinity</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>76.207.531-8</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="n">
+        <v>8555.75</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1197-123-CM26</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>61.107.000-4</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Transporte Corporativo Infinity</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>76.207.531-8</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="n">
+        <v>6260.3</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>1059109-94-CM26</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>61.107.000-4</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Julio Saavedra</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>76.248.427-7</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="n">
+        <v>30258.13</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>933-95-CM26</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>61.107.000-4</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="n">
+        <v>317.17</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>1077367-61-CM26</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>61.607.301-k</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>TURISMO AYEKANTUN LIMITADA</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>76.470.279-4</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="n">
+        <v>41230.37</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>1057417-16197-CM26</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>61.607.301-K</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>TURISMO AYEKANTUN LIMITADA</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>76.470.279-4</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="n">
+        <v>22013.99</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>1059109-101-CM26</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>61.107.000-4</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Felipe </t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>76.834.013-7</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="n">
+        <v>926.26</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-top-organismos/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos.xlsx
+++ b/docs/oc-top-organismos/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M80"/>
+  <dimension ref="A1:M78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2123-55-CM26</t>
+          <t>1057417-10664-CM26</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-03-28</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,27 +539,27 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>61.607.301-K</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>GUILLERMO MANUEL VARGAS BARRAZA</t>
+          <t>TRANSPORTES MONSALVE Y COMPAÑIA LIMITADA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>7.235.925-9</t>
+          <t>76.701.245-4</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>12760.36</v>
+        <v>34533.22</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1057417-10664-CM26</t>
+          <t>1057417-10665-CM26</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>34533.22</v>
+        <v>26393.09</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1057417-10665-CM26</t>
+          <t>1057417-10698-CM26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>26393.09</v>
+        <v>63924.39</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1057417-10698-CM26</t>
+          <t>1057417-10699-CM26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>TRANSPORTES MONSALVE Y COMPAÑIA LIMITADA</t>
+          <t>Transportes Luis Rifo y compañia limitada</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>76.701.245-4</t>
+          <t>76.114.087-6</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>63924.39</v>
+        <v>40321.27</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1057417-10699-CM26</t>
+          <t>2069-3343-CM26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -773,37 +773,37 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>61.607.301-K</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Transportes Luis Rifo y compañia limitada</t>
+          <t xml:space="preserve">PESCO RENTAL SOCIEDAD ANONIMA </t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>76.114.087-6</t>
+          <t>76.238.635-6</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>40321.27</v>
+        <v>611308.61</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2123-61-CM26</t>
+          <t>934-45-CM26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -834,53 +834,57 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>FEBGIP SPA</t>
+          <t>PAULA ANDREA MERY NAVIA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>77.864.159-3</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
+          <t>11.844.234-2</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>46307.26</v>
+        <v>1216.48</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1671-56-CM26</t>
+          <t>997-52-CM26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,12 +894,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -905,27 +909,27 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>INVERSIONES Y TRANSPORTES SAYEN SPA</t>
+          <t>Sociedad Comercial de Transporte ICT Limitada</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>76.438.029-0</t>
+          <t>76.070.302-8</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +939,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>11699.16</v>
+        <v>61853.9</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2069-3343-CM26</t>
+          <t>1176-39-CM26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,12 +955,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -966,27 +970,27 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t xml:space="preserve">PESCO RENTAL SOCIEDAD ANONIMA </t>
+          <t>INVERSIONES MTEA SPA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>76.238.635-6</t>
+          <t>76.366.361-2</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +1000,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>611308.61</v>
+        <v>23758.03</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>934-45-CM26</t>
+          <t>930-85-CM26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1012,17 +1016,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1037,17 +1041,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>PAULA ANDREA MERY NAVIA</t>
+          <t>JOSUE MANUEL</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>11.844.234-2</t>
+          <t>76.370.023-2</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1061,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>1216.48</v>
+        <v>1733.6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>997-52-CM26</t>
+          <t>299-85-CM26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1078,37 +1082,37 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Sociedad Comercial de Transporte ICT Limitada</t>
+          <t>Julio Saavedra</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>76.070.302-8</t>
+          <t>76.248.427-7</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1122,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>61853.9</v>
+        <v>53120.63</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1176-39-CM26</t>
+          <t>1434-94-CM26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1139,7 +1143,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1149,27 +1153,27 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.104.022-9</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>INVERSIONES MTEA SPA</t>
+          <t>SMC</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>76.366.361-2</t>
+          <t>76.310.505-9</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1183,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>23758.03</v>
+        <v>403185.16</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>162-194-CM26</t>
+          <t>1488-545-CM26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1195,12 +1199,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1210,27 +1214,27 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>61.602.232-6</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>VIVANET</t>
+          <t>TRANSERVI JL SPA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>76.018.259-1</t>
+          <t>77.063.031-2</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,13 +1244,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>40387.43</v>
+        <v>64684.58</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>930-85-CM26</t>
+          <t>1488-546-CM26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1256,12 +1260,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1271,27 +1275,27 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.602.232-6</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>JOSUE MANUEL</t>
+          <t>TRANSERVI JL SPA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>76.370.023-2</t>
+          <t>77.063.031-2</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,13 +1305,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>1733.6</v>
+        <v>27721.96</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>299-85-CM26</t>
+          <t>1488-639-CM26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1317,42 +1321,42 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.602.232-6</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Julio Saavedra</t>
+          <t>TRANSERVI JL SPA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>76.248.427-7</t>
+          <t>77.063.031-2</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1366,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>53120.63</v>
+        <v>25279.97</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1434-94-CM26</t>
+          <t>934-81-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1378,12 +1382,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1393,43 +1397,47 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>61.104.022-9</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>SMC</t>
+          <t>PAULA ANDREA MERY NAVIA</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>76.310.505-9</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
+          <t>11.844.234-2</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>403185.16</v>
+        <v>1548.17</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>162-205-CM26</t>
+          <t>1392-57-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1444,37 +1452,37 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>61.104.000-8</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>VIVANET</t>
+          <t>AUTOMOTRIZ R Y R LIMITADA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>76.018.259-1</t>
+          <t>77.951.690-3</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,13 +1492,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>36943.03</v>
+        <v>12017.6</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1488-546-CM26</t>
+          <t>997-77-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1505,37 +1513,37 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>61.602.232-6</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>TRANSERVI JL SPA</t>
+          <t>Sociedad Comercial de Transporte ICT Limitada</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>77.063.031-2</t>
+          <t>76.070.302-8</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,13 +1553,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>27721.96</v>
+        <v>33120.62</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1488-639-CM26</t>
+          <t>1196-138-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1566,37 +1574,37 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>61.602.232-6</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>TRANSERVI JL SPA</t>
+          <t>JOSUE MANUEL</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>77.063.031-2</t>
+          <t>76.370.023-2</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,13 +1614,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>25279.97</v>
+        <v>6911.17</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1488-545-CM26</t>
+          <t>299-107-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1627,7 +1635,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1637,27 +1645,27 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>61.602.232-6</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>TRANSERVI JL SPA</t>
+          <t>Julio Saavedra</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>77.063.031-2</t>
+          <t>76.248.427-7</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,13 +1675,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>64684.58</v>
+        <v>1627.92</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>934-81-CM26</t>
+          <t>4215-17-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1688,7 +1696,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1698,12 +1706,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.104.022-9</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1721,20 +1729,24 @@
           <t>11.844.234-2</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>1548.17</v>
+        <v>75.89</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1392-57-CM26</t>
+          <t>934-82-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1749,53 +1761,57 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>61.104.000-8</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ R Y R LIMITADA</t>
+          <t>PAULA ANDREA MERY NAVIA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>77.951.690-3</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
+          <t>11.844.234-2</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>12017.6</v>
+        <v>1626.3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>997-77-CM26</t>
+          <t>4215-18-SE26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1810,7 +1826,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1820,43 +1836,47 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.104.022-9</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Sociedad Comercial de Transporte ICT Limitada</t>
+          <t>PAULA ANDREA MERY NAVIA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>76.070.302-8</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
+          <t>11.844.234-2</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>33120.62</v>
+        <v>84491.62</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1196-138-CM26</t>
+          <t>934-85-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1871,7 +1891,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1891,17 +1911,17 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>JOSUE MANUEL</t>
+          <t>ALEXANDER SEBASTIÁN BERG KROLL</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>76.370.023-2</t>
+          <t>8.148.859-2</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,13 +1931,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>6911.17</v>
+        <v>31224.93</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>299-107-CM26</t>
+          <t>1062807-63-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1932,37 +1952,37 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>62.000.590-8</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION REGION ÑUBLE</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Julio Saavedra</t>
+          <t>David Isaac</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>76.248.427-7</t>
+          <t>76.820.816-6</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1972,13 +1992,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>1627.92</v>
+        <v>216839.78</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1062807-63-CM26</t>
+          <t>1057417-13722-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1988,42 +2008,42 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>62.000.590-8</t>
+          <t>61.607.301-K</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION REGION ÑUBLE</t>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>David Isaac</t>
+          <t>TRANSPORTES MONSALVE Y COMPAÑIA LIMITADA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>76.820.816-6</t>
+          <t>76.701.245-4</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2033,13 +2053,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>216839.78</v>
+        <v>40430.05</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>934-85-CM26</t>
+          <t>934-86-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2049,12 +2069,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2079,28 +2099,32 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>ALEXANDER SEBASTIÁN BERG KROLL</t>
+          <t>TRANSPORTES RUTAMUSIC LIMITADA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>8.148.859-2</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
+          <t>76.735.787-7</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>31224.93</v>
+        <v>6939.85</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>4215-17-CM26</t>
+          <t>2735-872-SE26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2110,58 +2134,62 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.104.022-9</t>
+          <t>69.255.200-8</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>I MUNICIPALIDAD LO BARNECHEA</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>PAULA ANDREA MERY NAVIA</t>
+          <t>CONSTRUCTORA E INGENIERIA ELISEO SPA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>11.844.234-2</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
+          <t>76.366.537-2</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>75.89</v>
+        <v>28920.36</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>934-82-CM26</t>
+          <t>2735-850-SE26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2171,12 +2199,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2186,43 +2214,47 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>69.255.200-8</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>I MUNICIPALIDAD LO BARNECHEA</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>PAULA ANDREA MERY NAVIA</t>
+          <t>CONSTRUCTORA E INGENIERIA ELISEO SPA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>11.844.234-2</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
+          <t>76.366.537-2</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>1626.3</v>
+        <v>82539.53</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1057417-13722-CM26</t>
+          <t>997-96-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2237,37 +2269,37 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>61.607.301-K</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>TRANSPORTES MONSALVE Y COMPAÑIA LIMITADA</t>
+          <t>Sociedad Comercial de Transporte ICT Limitada</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>76.701.245-4</t>
+          <t>76.070.302-8</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
@@ -2277,13 +2309,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>40430.05</v>
+        <v>10483.56</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>934-86-CM26</t>
+          <t>2735-849-SE26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2298,53 +2330,57 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>69.255.200-8</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>I MUNICIPALIDAD LO BARNECHEA</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>TRANSPORTES RUTAMUSIC LIMITADA</t>
+          <t>CONSTRUCTORA E INGENIERIA ELISEO SPA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>76.735.787-7</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
+          <t>76.366.537-2</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>6939.85</v>
+        <v>38722.38</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>997-96-CM26</t>
+          <t>934-88-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2359,7 +2395,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2369,43 +2405,47 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Sociedad Comercial de Transporte ICT Limitada</t>
+          <t>PAULA ANDREA MERY NAVIA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>76.070.302-8</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
+          <t>11.844.234-2</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>10483.56</v>
+        <v>8605.07</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>934-88-CM26</t>
+          <t>1178-37-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2420,7 +2460,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2430,27 +2470,27 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>PAULA ANDREA MERY NAVIA</t>
+          <t>INVERSIONES MTEA SPA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>11.844.234-2</t>
+          <t>76.366.361-2</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -2460,7 +2500,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>8605.07</v>
+        <v>46114.6</v>
       </c>
     </row>
     <row r="34">
@@ -2527,7 +2567,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1178-37-CM26</t>
+          <t>1197-87-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2552,27 +2592,27 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>INVERSIONES MTEA SPA</t>
+          <t>Transporte Corporativo Infinity</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>76.366.361-2</t>
+          <t>76.207.531-8</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2582,13 +2622,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>46114.6</v>
+        <v>13993.69</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1197-87-CM26</t>
+          <t>5751-168-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2603,7 +2643,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2613,37 +2653,41 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.818.002-6</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION DE V</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Transporte Corporativo Infinity</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>76.207.531-8</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>13993.69</v>
+        <v>194424.62</v>
       </c>
     </row>
     <row r="37">
@@ -2710,7 +2754,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>5751-168-CM26</t>
+          <t>1523-1545-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2725,7 +2769,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2735,27 +2779,27 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>61.818.002-6</t>
+          <t>61.602.236-9</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION DE V</t>
+          <t>SERVICIO NACIONAL ARAUCANIA SUR HOSPITAL DR ABRAHAM GODOY PENA LAUTARO</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>TRANSERVI JL SPA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
+          <t>77.063.031-2</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
@@ -2765,13 +2809,13 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>194424.62</v>
+        <v>12330.98</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1523-1545-CM26</t>
+          <t>930-147-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2786,7 +2830,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2796,27 +2840,27 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>61.602.236-9</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL ARAUCANIA SUR HOSPITAL DR ABRAHAM GODOY PENA LAUTARO</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>TRANSERVI JL SPA</t>
+          <t>JOSUE MANUEL</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>77.063.031-2</t>
+          <t>76.370.023-2</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
@@ -2826,13 +2870,13 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>12330.98</v>
+        <v>5139.63</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>930-147-CM26</t>
+          <t>1488-1053-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2847,37 +2891,37 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.602.232-6</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>JOSUE MANUEL</t>
+          <t>TRANSERVI JL SPA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>76.370.023-2</t>
+          <t>77.063.031-2</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2887,13 +2931,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>5139.63</v>
+        <v>64308.63</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2078-924-CM26</t>
+          <t>934-94-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2908,7 +2952,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2918,43 +2962,47 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>CAROLYN MARLEN</t>
+          <t>PAULA ANDREA MERY NAVIA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>76.905.851-6</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
+          <t>11.844.234-2</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>16061.33</v>
+        <v>18116.72</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1488-1053-CM26</t>
+          <t>299-124-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2969,37 +3017,37 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>61.602.232-6</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>TRANSERVI JL SPA</t>
+          <t>CAR PLACE SPA</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>77.063.031-2</t>
+          <t>76.704.974-9</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3009,13 +3057,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>64308.63</v>
+        <v>10018.6</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>934-94-CM26</t>
+          <t>1057417-14563-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3030,7 +3078,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3040,27 +3088,27 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.607.301-K</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>PAULA ANDREA MERY NAVIA</t>
+          <t>TRANSPORTES MONSALVE Y COMPAÑIA LIMITADA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>11.844.234-2</t>
+          <t>76.701.245-4</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3070,13 +3118,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>18116.72</v>
+        <v>43703.37</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>5602-184-CM26</t>
+          <t>1488-903-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3086,42 +3134,42 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>61.602.232-6</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>AUTORENTAS DEL PACIFICO SPA</t>
+          <t>TRANSERVI JL SPA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>83.547.100-4</t>
+          <t>77.063.031-2</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3131,13 +3179,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>9303.450000000001</v>
+        <v>208859.42</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>299-124-CM26</t>
+          <t>1488-904-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3147,42 +3195,42 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.602.232-6</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>CAR PLACE SPA</t>
+          <t>TRANSERVI JL SPA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>76.704.974-9</t>
+          <t>77.063.031-2</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3192,13 +3240,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>10018.6</v>
+        <v>83035.34</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1057417-14563-CM26</t>
+          <t>1178-45-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3208,12 +3256,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3223,27 +3271,27 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>61.607.301-K</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>TRANSPORTES MONSALVE Y COMPAÑIA LIMITADA</t>
+          <t>INVERSIONES MTEA SPA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>76.701.245-4</t>
+          <t>76.366.361-2</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3253,13 +3301,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>43703.37</v>
+        <v>183957.01</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>934-114-CM26</t>
+          <t>932-136-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3294,17 +3342,17 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>PAULA ANDREA MERY NAVIA</t>
+          <t>Sociedad de Transporte Jiménez Hermanos Ltda.</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>11.844.234-2</t>
+          <t>76.036.979-9</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -3314,13 +3362,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>2594.9</v>
+        <v>2350.12</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1178-45-CM26</t>
+          <t>934-114-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3345,43 +3393,47 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>INVERSIONES MTEA SPA</t>
+          <t>PAULA ANDREA MERY NAVIA</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>76.366.361-2</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr"/>
+          <t>11.844.234-2</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>183957.01</v>
+        <v>2594.9</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>932-136-CM26</t>
+          <t>932-138-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3396,12 +3448,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3436,13 +3488,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>2350.12</v>
+        <v>21934.59</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1488-903-CM26</t>
+          <t>1057417-14549-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3457,37 +3509,37 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>61.602.232-6</t>
+          <t>61.607.301-K</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>TRANSERVI JL SPA</t>
+          <t>Transportes Luis Rifo y compañia limitada</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>77.063.031-2</t>
+          <t>76.114.087-6</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3497,13 +3549,13 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>208859.42</v>
+        <v>37143.95</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1488-904-CM26</t>
+          <t>1057417-14604-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3518,37 +3570,37 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>61.602.232-6</t>
+          <t>61.607.301-K</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>TRANSERVI JL SPA</t>
+          <t>Transportes Luis Rifo y compañia limitada</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>77.063.031-2</t>
+          <t>76.114.087-6</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -3558,13 +3610,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>83035.34</v>
+        <v>3535.96</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>932-138-CM26</t>
+          <t>1197-97-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3579,7 +3631,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3599,17 +3651,17 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Sociedad de Transporte Jiménez Hermanos Ltda.</t>
+          <t>Transporte Corporativo Infinity</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>76.036.979-9</t>
+          <t>76.207.531-8</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -3619,13 +3671,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>21934.59</v>
+        <v>15278.84</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1057417-14549-CM26</t>
+          <t>934-131-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3640,53 +3692,57 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>61.607.301-K</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Transportes Luis Rifo y compañia limitada</t>
+          <t>PAULA ANDREA MERY NAVIA</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>76.114.087-6</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
+          <t>11.844.234-2</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>37143.95</v>
+        <v>2960.53</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1057417-14604-CM26</t>
+          <t>1197-99-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3701,7 +3757,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3711,27 +3767,27 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>61.607.301-K</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Transportes Luis Rifo y compañia limitada</t>
+          <t>CAR PLACE SPA</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>76.114.087-6</t>
+          <t>76.704.974-9</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -3741,13 +3797,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>3535.96</v>
+        <v>27355.86</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1197-97-CM26</t>
+          <t>1523-1816-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3762,37 +3818,37 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.602.236-9</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>SERVICIO NACIONAL ARAUCANIA SUR HOSPITAL DR ABRAHAM GODOY PENA LAUTARO</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Transporte Corporativo Infinity</t>
+          <t>LUIS ALBERTO PAILLAMILLA OÑATE</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>76.207.531-8</t>
+          <t>16.995.419-4</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3802,13 +3858,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>15278.84</v>
+        <v>249028.09</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>934-131-CM26</t>
+          <t>934-134-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3823,12 +3879,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3856,20 +3912,24 @@
           <t>11.844.234-2</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>2960.53</v>
+        <v>3942.4</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1523-1816-CM26</t>
+          <t>934-136-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3884,53 +3944,57 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>61.602.236-9</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL ARAUCANIA SUR HOSPITAL DR ABRAHAM GODOY PENA LAUTARO</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>LUIS ALBERTO PAILLAMILLA OÑATE</t>
+          <t>TURISMO Y EXCURSIONES PATAGON AUSTRAL SPA</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>16.995.419-4</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
+          <t>77.659.446-6</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>249028.09</v>
+        <v>878.41</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1197-99-CM26</t>
+          <t>1198-203-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3945,7 +4009,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3965,17 +4029,17 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>CAR PLACE SPA</t>
+          <t xml:space="preserve">Felipe </t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>76.704.974-9</t>
+          <t>76.834.013-7</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -3985,13 +4049,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>27355.86</v>
+        <v>5193.3</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>934-134-CM26</t>
+          <t>1057417-15339-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4006,7 +4070,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4016,27 +4080,27 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.607.301-K</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>PAULA ANDREA MERY NAVIA</t>
+          <t>TURISMO AYEKANTUN LIMITADA</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>11.844.234-2</t>
+          <t>76.470.279-4</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -4046,13 +4110,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>3942.4</v>
+        <v>42076.74</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>934-136-CM26</t>
+          <t>932-152-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4067,12 +4131,12 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -4087,17 +4151,17 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>TURISMO Y EXCURSIONES PATAGON AUSTRAL SPA</t>
+          <t>Sociedad de Transporte Jiménez Hermanos Ltda.</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>77.659.446-6</t>
+          <t>76.036.979-9</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4107,13 +4171,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>878.41</v>
+        <v>17149.02</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1198-203-CM26</t>
+          <t>932-155-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4128,7 +4192,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4148,17 +4212,17 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Felipe </t>
+          <t>CAR PLACE SPA</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>76.834.013-7</t>
+          <t>76.704.974-9</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -4168,13 +4232,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>5193.3</v>
+        <v>35882.19</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1057417-15339-CM26</t>
+          <t>1197-107-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4189,7 +4253,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4199,27 +4263,27 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>61.607.301-K</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>TURISMO AYEKANTUN LIMITADA</t>
+          <t xml:space="preserve">Felipe </t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>76.470.279-4</t>
+          <t>76.834.013-7</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4229,13 +4293,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>42076.74</v>
+        <v>1452.68</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>932-152-CM26</t>
+          <t>1488-1234-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4245,12 +4309,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4260,27 +4324,27 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.602.232-6</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Sociedad de Transporte Jiménez Hermanos Ltda.</t>
+          <t>TRANSERVI JL SPA</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>76.036.979-9</t>
+          <t>77.063.031-2</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -4290,13 +4354,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>17149.02</v>
+        <v>46989.46</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>932-155-CM26</t>
+          <t>1199-213-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4306,12 +4370,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4331,17 +4395,17 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>CAR PLACE SPA</t>
+          <t>BUSES VILLAR</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>76.704.974-9</t>
+          <t>76.465.610-5</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
@@ -4351,13 +4415,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>35882.19</v>
+        <v>38554.16</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1197-107-CM26</t>
+          <t>299-168-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4367,12 +4431,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4392,17 +4456,17 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Felipe </t>
+          <t>CAR PLACE SPA</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>76.834.013-7</t>
+          <t>76.704.974-9</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -4412,13 +4476,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>1452.68</v>
+        <v>77200.13</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1488-1234-CM26</t>
+          <t>931-165-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4433,7 +4497,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4443,27 +4507,27 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>61.602.232-6</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>TRANSERVI JL SPA</t>
+          <t>JOSUE MANUEL</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>77.063.031-2</t>
+          <t>76.370.023-2</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
@@ -4473,13 +4537,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>46989.46</v>
+        <v>20647.27</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1199-213-CM26</t>
+          <t>933-88-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4494,7 +4558,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4514,17 +4578,17 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>BUSES VILLAR</t>
+          <t>TURISMO AYEKANTUN LIMITADA</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>76.465.610-5</t>
+          <t>76.470.279-4</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
@@ -4534,13 +4598,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>38554.16</v>
+        <v>3841.35</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>299-168-CM26</t>
+          <t>933-70-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4555,12 +4619,12 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -4575,17 +4639,17 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>CAR PLACE SPA</t>
+          <t>TURISMO AYEKANTUN LIMITADA</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>76.704.974-9</t>
+          <t>76.470.279-4</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
@@ -4595,13 +4659,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>77200.13</v>
+        <v>85024.07000000001</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>933-88-CM26</t>
+          <t>1059109-94-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4616,7 +4680,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4636,17 +4700,17 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>TURISMO AYEKANTUN LIMITADA</t>
+          <t>Julio Saavedra</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>76.470.279-4</t>
+          <t>76.248.427-7</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
@@ -4656,13 +4720,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>3841.35</v>
+        <v>30258.13</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>931-165-CM26</t>
+          <t>1197-123-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4677,7 +4741,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4697,17 +4761,17 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>JOSUE MANUEL</t>
+          <t>Transporte Corporativo Infinity</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>76.370.023-2</t>
+          <t>76.207.531-8</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
@@ -4717,13 +4781,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>20647.27</v>
+        <v>6260.3</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>933-70-CM26</t>
+          <t>2735-1056-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4738,53 +4802,57 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>69.255.200-8</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>I MUNICIPALIDAD LO BARNECHEA</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>TURISMO AYEKANTUN LIMITADA</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>76.470.279-4</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr"/>
+          <t>76.148.628-4</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>85024.07000000001</v>
+        <v>55142.84</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2123-317-CM26</t>
+          <t>931-167-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4799,7 +4867,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4809,27 +4877,27 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Empresa de Transportes Pablo Jaramillo Benavente E</t>
+          <t>CAR PLACE SPA</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>76.076.244-k</t>
+          <t>76.704.974-9</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
@@ -4839,13 +4907,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>10096.61</v>
+        <v>9912.15</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>931-167-CM26</t>
+          <t>1197-122-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4880,17 +4948,17 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>CAR PLACE SPA</t>
+          <t>Transporte Corporativo Infinity</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>76.704.974-9</t>
+          <t>76.207.531-8</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
@@ -4900,13 +4968,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>9912.15</v>
+        <v>8555.75</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1197-122-CM26</t>
+          <t>933-95-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4921,7 +4989,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4941,33 +5009,37 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Transporte Corporativo Infinity</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>76.207.531-8</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr"/>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>8555.75</v>
+        <v>317.17</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1197-123-CM26</t>
+          <t>1077367-61-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4982,7 +5054,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4992,27 +5064,27 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.607.301-k</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Transporte Corporativo Infinity</t>
+          <t>TURISMO AYEKANTUN LIMITADA</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>76.207.531-8</t>
+          <t>76.470.279-4</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
@@ -5022,13 +5094,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>6260.3</v>
+        <v>41230.37</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1059109-94-CM26</t>
+          <t>2735-1197-CM26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5043,7 +5115,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5053,27 +5125,27 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>69.255.200-8</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>I MUNICIPALIDAD LO BARNECHEA</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Julio Saavedra</t>
+          <t>AUTOMOTRIZ R Y R LIMITADA</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>76.248.427-7</t>
+          <t>77.951.690-3</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
@@ -5083,13 +5155,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>30258.13</v>
+        <v>27536.25</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>933-95-CM26</t>
+          <t>1057417-16197-CM26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5104,7 +5176,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5114,12 +5186,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.607.301-K</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5129,12 +5201,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>TURISMO AYEKANTUN LIMITADA</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
+          <t>76.470.279-4</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
@@ -5144,13 +5216,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>317.17</v>
+        <v>22013.99</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1077367-61-CM26</t>
+          <t>1059109-101-CM26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5165,7 +5237,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -5175,27 +5247,27 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>61.607.301-k</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>TURISMO AYEKANTUN LIMITADA</t>
+          <t xml:space="preserve">Felipe </t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>76.470.279-4</t>
+          <t>76.834.013-7</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
@@ -5205,128 +5277,6 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>41230.37</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>1057417-16197-CM26</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>2239-12-LR25</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>sep-2026</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>61.607.301-K</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Biobío</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>TURISMO AYEKANTUN LIMITADA</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>76.470.279-4</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M79" s="2" t="n">
-        <v>22013.99</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>1059109-101-CM26</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>2239-12-LR25</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>sep-2026</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>61.107.000-4</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Ñuble</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Felipe </t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>76.834.013-7</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M80" s="2" t="n">
         <v>926.26</v>
       </c>
     </row>

--- a/docs/oc-top-organismos/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos.xlsx
+++ b/docs/oc-top-organismos/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M78"/>
+  <dimension ref="A1:M87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1057417-10664-CM26</t>
+          <t>1057417-10698-CM26</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -562,20 +562,24 @@
           <t>76.701.245-4</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>34533.22</v>
+        <v>63924.39</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1057417-10665-CM26</t>
+          <t>1057417-10699-CM26</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -615,12 +619,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>TRANSPORTES MONSALVE Y COMPAÑIA LIMITADA</t>
+          <t>Transportes Luis Rifo y compañia limitada</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>76.701.245-4</t>
+          <t>76.114.087-6</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +634,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>26393.09</v>
+        <v>40321.27</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1057417-10698-CM26</t>
+          <t>1057417-10665-CM26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -684,20 +688,24 @@
           <t>76.701.245-4</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>63924.39</v>
+        <v>26393.09</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1057417-10699-CM26</t>
+          <t>1057417-10664-CM26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -737,22 +745,26 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Transportes Luis Rifo y compañia limitada</t>
+          <t>TRANSPORTES MONSALVE Y COMPAÑIA LIMITADA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>76.114.087-6</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
+          <t>76.701.245-4</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>40321.27</v>
+        <v>34533.22</v>
       </c>
     </row>
     <row r="6">
@@ -1189,7 +1201,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1488-545-CM26</t>
+          <t>1488-546-CM26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1244,13 +1256,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>64684.58</v>
+        <v>27721.96</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1488-546-CM26</t>
+          <t>1488-545-CM26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1305,7 +1317,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>27721.96</v>
+        <v>64684.58</v>
       </c>
     </row>
     <row r="15">
@@ -1498,7 +1510,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>997-77-CM26</t>
+          <t>1413021-18-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1523,27 +1535,27 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>60.804.011-0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Sociedad Comercial de Transporte ICT Limitada</t>
+          <t xml:space="preserve">Felipe </t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>76.070.302-8</t>
+          <t>76.834.013-7</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1553,7 +1565,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>33120.62</v>
+        <v>21959.86</v>
       </c>
     </row>
     <row r="19">
@@ -1620,7 +1632,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>299-107-CM26</t>
+          <t>997-77-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1635,37 +1647,37 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Julio Saavedra</t>
+          <t>Sociedad Comercial de Transporte ICT Limitada</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>76.248.427-7</t>
+          <t>76.070.302-8</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1675,13 +1687,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>1627.92</v>
+        <v>33120.62</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>4215-17-CM26</t>
+          <t>299-107-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1696,57 +1708,53 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>61.104.022-9</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>PAULA ANDREA MERY NAVIA</t>
+          <t>Julio Saavedra</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>11.844.234-2</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>Los Lagos</t>
-        </is>
-      </c>
+          <t>76.248.427-7</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>75.89</v>
+        <v>1627.92</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>934-82-CM26</t>
+          <t>4215-17-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1766,17 +1774,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.104.022-9</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1805,13 +1813,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>1626.3</v>
+        <v>75.89</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>4215-18-SE26</t>
+          <t>934-82-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1831,17 +1839,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>61.104.022-9</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1870,13 +1878,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>84491.62</v>
+        <v>1626.3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>934-85-CM26</t>
+          <t>4215-18-SE26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1901,12 +1909,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.104.022-9</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1916,22 +1924,26 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>ALEXANDER SEBASTIÁN BERG KROLL</t>
+          <t>PAULA ANDREA MERY NAVIA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>8.148.859-2</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
+          <t>11.844.234-2</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>31224.93</v>
+        <v>84491.62</v>
       </c>
     </row>
     <row r="25">
@@ -1998,7 +2010,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1057417-13722-CM26</t>
+          <t>934-85-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2008,42 +2020,42 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>61.607.301-K</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>TRANSPORTES MONSALVE Y COMPAÑIA LIMITADA</t>
+          <t>ALEXANDER SEBASTIÁN BERG KROLL</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>76.701.245-4</t>
+          <t>8.148.859-2</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2053,13 +2065,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>40430.05</v>
+        <v>31224.93</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>934-86-CM26</t>
+          <t>1057417-13722-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2079,37 +2091,37 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.607.301-K</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>TRANSPORTES RUTAMUSIC LIMITADA</t>
+          <t>TRANSPORTES MONSALVE Y COMPAÑIA LIMITADA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>76.735.787-7</t>
+          <t>76.701.245-4</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2118,13 +2130,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>6939.85</v>
+        <v>40430.05</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2735-872-SE26</t>
+          <t>934-86-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2139,57 +2151,57 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>69.255.200-8</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD LO BARNECHEA</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>TRANSPORTES RUTAMUSIC LIMITADA</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>76.735.787-7</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
           <t>Metropolitana</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>CONSTRUCTORA E INGENIERIA ELISEO SPA</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>76.366.537-2</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>28920.36</v>
+        <v>6939.85</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2735-850-SE26</t>
+          <t>997-96-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2209,52 +2221,48 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>69.255.200-8</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD LO BARNECHEA</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>CONSTRUCTORA E INGENIERIA ELISEO SPA</t>
+          <t>Sociedad Comercial de Transporte ICT Limitada</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>76.366.537-2</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.070.302-8</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>82539.53</v>
+        <v>10483.56</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>997-96-CM26</t>
+          <t>2735-850-SE26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2274,48 +2282,52 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.255.200-8</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD LO BARNECHEA</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Sociedad Comercial de Transporte ICT Limitada</t>
+          <t>CONSTRUCTORA E INGENIERIA ELISEO SPA</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>76.070.302-8</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
+          <t>76.366.537-2</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>10483.56</v>
+        <v>82539.53</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2735-849-SE26</t>
+          <t>2735-872-SE26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2374,13 +2386,13 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>38722.38</v>
+        <v>28920.36</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>934-88-CM26</t>
+          <t>2735-849-SE26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2395,42 +2407,42 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>69.255.200-8</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>I MUNICIPALIDAD LO BARNECHEA</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>PAULA ANDREA MERY NAVIA</t>
+          <t>CONSTRUCTORA E INGENIERIA ELISEO SPA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>11.844.234-2</t>
+          <t>76.366.537-2</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2439,13 +2451,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>8605.07</v>
+        <v>38722.38</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1178-37-CM26</t>
+          <t>934-88-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2460,7 +2472,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2470,43 +2482,47 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>INVERSIONES MTEA SPA</t>
+          <t>PAULA ANDREA MERY NAVIA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>76.366.361-2</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
+          <t>11.844.234-2</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>46114.6</v>
+        <v>8605.07</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1196-151-CM26</t>
+          <t>1178-37-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2531,27 +2547,27 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>JOSUE MANUEL</t>
+          <t>INVERSIONES MTEA SPA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>76.370.023-2</t>
+          <t>76.366.361-2</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2561,7 +2577,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>3767.53</v>
+        <v>46114.6</v>
       </c>
     </row>
     <row r="35">
@@ -2628,7 +2644,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>5751-168-CM26</t>
+          <t>1196-151-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2643,7 +2659,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2653,41 +2669,37 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>61.818.002-6</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION DE V</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>JOSUE MANUEL</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
+          <t>76.370.023-2</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>194424.62</v>
+        <v>3767.53</v>
       </c>
     </row>
     <row r="37">
@@ -3111,7 +3123,11 @@
           <t>76.701.245-4</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3140,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1488-903-CM26</t>
+          <t>932-136-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3144,32 +3160,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>61.602.232-6</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>TRANSERVI JL SPA</t>
+          <t>Sociedad de Transporte Jiménez Hermanos Ltda.</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>77.063.031-2</t>
+          <t>76.036.979-9</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
@@ -3179,13 +3195,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>208859.42</v>
+        <v>2350.12</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1488-904-CM26</t>
+          <t>1178-45-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3205,32 +3221,32 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>61.602.232-6</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>TRANSERVI JL SPA</t>
+          <t>INVERSIONES MTEA SPA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>77.063.031-2</t>
+          <t>76.366.361-2</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
@@ -3240,13 +3256,13 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>83035.34</v>
+        <v>183957.01</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1178-45-CM26</t>
+          <t>1488-904-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3266,32 +3282,32 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.602.232-6</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>INVERSIONES MTEA SPA</t>
+          <t>TRANSERVI JL SPA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>76.366.361-2</t>
+          <t>77.063.031-2</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3301,13 +3317,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>183957.01</v>
+        <v>83035.34</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>932-136-CM26</t>
+          <t>1488-903-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3327,32 +3343,32 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.602.232-6</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Sociedad de Transporte Jiménez Hermanos Ltda.</t>
+          <t>TRANSERVI JL SPA</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>76.036.979-9</t>
+          <t>77.063.031-2</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -3362,7 +3378,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>2350.12</v>
+        <v>208859.42</v>
       </c>
     </row>
     <row r="48">
@@ -3494,7 +3510,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>1057417-14549-CM26</t>
+          <t>1197-97-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3514,32 +3530,32 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>61.607.301-K</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Transportes Luis Rifo y compañia limitada</t>
+          <t>Transporte Corporativo Infinity</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>76.114.087-6</t>
+          <t>76.207.531-8</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
@@ -3549,7 +3565,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>37143.95</v>
+        <v>15278.84</v>
       </c>
     </row>
     <row r="51">
@@ -3616,7 +3632,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1197-97-CM26</t>
+          <t>1057417-14549-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3636,32 +3652,32 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.607.301-K</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Transporte Corporativo Infinity</t>
+          <t>Transportes Luis Rifo y compañia limitada</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>76.207.531-8</t>
+          <t>76.114.087-6</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -3671,7 +3687,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>15278.84</v>
+        <v>37143.95</v>
       </c>
     </row>
     <row r="53">
@@ -3742,7 +3758,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1197-99-CM26</t>
+          <t>934-134-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3777,27 +3793,31 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>CAR PLACE SPA</t>
+          <t>PAULA ANDREA MERY NAVIA</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>76.704.974-9</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
+          <t>11.844.234-2</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>27355.86</v>
+        <v>3942.4</v>
       </c>
     </row>
     <row r="55">
@@ -3864,7 +3884,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>934-134-CM26</t>
+          <t>1197-99-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3899,31 +3919,27 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>PAULA ANDREA MERY NAVIA</t>
+          <t>CAR PLACE SPA</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>11.844.234-2</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>Los Lagos</t>
-        </is>
-      </c>
+          <t>76.704.974-9</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>3942.4</v>
+        <v>27355.86</v>
       </c>
     </row>
     <row r="57">
@@ -4319,7 +4335,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -4360,7 +4376,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1199-213-CM26</t>
+          <t>299-168-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4395,17 +4411,17 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>BUSES VILLAR</t>
+          <t>CAR PLACE SPA</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>76.465.610-5</t>
+          <t>76.704.974-9</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
@@ -4415,13 +4431,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>38554.16</v>
+        <v>77200.13</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>299-168-CM26</t>
+          <t>1199-213-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4456,17 +4472,17 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>CAR PLACE SPA</t>
+          <t>BUSES VILLAR</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>76.704.974-9</t>
+          <t>76.465.610-5</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -4476,7 +4492,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>77200.13</v>
+        <v>38554.16</v>
       </c>
     </row>
     <row r="66">
@@ -4502,7 +4518,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -4746,7 +4762,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -4787,7 +4803,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2735-1056-CM26</t>
+          <t>1197-122-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4807,52 +4823,48 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>69.255.200-8</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD LO BARNECHEA</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+          <t>Transporte Corporativo Infinity</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>76.148.628-4</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.207.531-8</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>55142.84</v>
+        <v>8555.75</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>931-167-CM26</t>
+          <t>2735-1056-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4877,43 +4889,47 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>69.255.200-8</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>I MUNICIPALIDAD LO BARNECHEA</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>CAR PLACE SPA</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>76.704.974-9</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr"/>
+          <t>76.148.628-4</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>9912.15</v>
+        <v>55142.84</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1197-122-CM26</t>
+          <t>931-167-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4933,7 +4949,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -4948,17 +4964,17 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Transporte Corporativo Infinity</t>
+          <t>CAR PLACE SPA</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>76.207.531-8</t>
+          <t>76.704.974-9</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
@@ -4968,7 +4984,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>8555.75</v>
+        <v>9912.15</v>
       </c>
     </row>
     <row r="74">
@@ -5024,7 +5040,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5039,7 +5055,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1077367-61-CM26</t>
+          <t>1057417-16197-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5064,7 +5080,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>61.607.301-k</t>
+          <t>61.607.301-K</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -5094,13 +5110,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>41230.37</v>
+        <v>22013.99</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2735-1197-CM26</t>
+          <t>1077367-61-CM26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5125,27 +5141,27 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>69.255.200-8</t>
+          <t>61.607.301-k</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD LO BARNECHEA</t>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ R Y R LIMITADA</t>
+          <t>TURISMO AYEKANTUN LIMITADA</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>77.951.690-3</t>
+          <t>76.470.279-4</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
@@ -5155,13 +5171,13 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>27536.25</v>
+        <v>41230.37</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1057417-16197-CM26</t>
+          <t>2735-1197-CM26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5186,27 +5202,27 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>61.607.301-K</t>
+          <t>69.255.200-8</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
+          <t>I MUNICIPALIDAD LO BARNECHEA</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>TURISMO AYEKANTUN LIMITADA</t>
+          <t>AUTOMOTRIZ R Y R LIMITADA</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>76.470.279-4</t>
+          <t>77.951.690-3</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
@@ -5216,7 +5232,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>22013.99</v>
+        <v>27536.25</v>
       </c>
     </row>
     <row r="78">
@@ -5242,7 +5258,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -5278,6 +5294,563 @@
       </c>
       <c r="M78" s="2" t="n">
         <v>926.26</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2069-8569-CM26</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>61.608.101-2</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PESCO RENTAL SOCIEDAD ANONIMA </t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>76.238.635-6</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="n">
+        <v>590228.25</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>932-173-CM26</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>61.107.000-4</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Sociedad de Transporte Jiménez Hermanos Ltda.</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>76.036.979-9</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="n">
+        <v>1859.18</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>1200-241-CM26</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>61.107.000-4</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>ALEXANDER SEBASTIÁN BERG KROLL</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>8.148.859-2</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="n">
+        <v>35338.24</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>1059109-109-CM26</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>61.107.000-4</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Julio Saavedra</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>76.248.427-7</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="n">
+        <v>44861.8</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>1200-252-CM26</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>61.107.000-4</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>ALEMOSO SPA</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>77.852.175-K</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="n">
+        <v>8299.43</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>1523-2401-CM26</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>61.602.236-9</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL ARAUCANIA SUR HOSPITAL DR ABRAHAM GODOY PENA LAUTARO</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>ALEXANDRO DAVID GONZÁLEZ SALAZAR</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>15.552.949-0</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="n">
+        <v>7699.87</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>1777-96-CM26</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>60.804.012-9</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>David Isaac</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>76.820.816-6</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="n">
+        <v>211983.43</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>934-198-CM26</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>61.107.000-4</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>CAR PLACE SPA</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>76.704.974-9</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="n">
+        <v>3565.43</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>1057417-17061-SE26</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>61.607.301-K</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>TRANSPORTES MONSALVE Y COMPAÑIA LIMITADA</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>76.701.245-4</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="n">
+        <v>314520.87</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-top-organismos/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos.xlsx
+++ b/docs/oc-top-organismos/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M87"/>
+  <dimension ref="A1:M88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -790,7 +790,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1591,7 +1591,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1969,7 +1969,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2221,7 +2221,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2262,7 +2262,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2735-850-SE26</t>
+          <t>2735-849-SE26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2321,7 +2321,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>82539.53</v>
+        <v>38722.38</v>
       </c>
     </row>
     <row r="31">
@@ -2392,7 +2392,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2735-849-SE26</t>
+          <t>2735-850-SE26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2451,7 +2451,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>38722.38</v>
+        <v>82539.53</v>
       </c>
     </row>
     <row r="33">
@@ -2583,7 +2583,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1197-87-CM26</t>
+          <t>1196-151-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2618,17 +2618,17 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Transporte Corporativo Infinity</t>
+          <t>JOSUE MANUEL</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>76.207.531-8</t>
+          <t>76.370.023-2</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2638,13 +2638,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>13993.69</v>
+        <v>3767.53</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1196-151-CM26</t>
+          <t>1197-87-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2679,17 +2679,17 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>JOSUE MANUEL</t>
+          <t>Transporte Corporativo Infinity</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>76.370.023-2</t>
+          <t>76.207.531-8</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
@@ -2699,7 +2699,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>3767.53</v>
+        <v>13993.69</v>
       </c>
     </row>
     <row r="37">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2847,7 +2847,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -3591,7 +3591,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -4010,7 +4010,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1198-203-CM26</t>
+          <t>934-137-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4025,12 +4025,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -4045,33 +4045,37 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Felipe </t>
+          <t>PAULA ANDREA MERY NAVIA</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>76.834.013-7</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr"/>
+          <t>11.844.234-2</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>5193.3</v>
+        <v>5292.15</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1057417-15339-CM26</t>
+          <t>1198-203-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4086,7 +4090,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4096,27 +4100,27 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>61.607.301-K</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>TURISMO AYEKANTUN LIMITADA</t>
+          <t xml:space="preserve">Felipe </t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>76.470.279-4</t>
+          <t>76.834.013-7</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -4126,13 +4130,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>42076.74</v>
+        <v>5193.3</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>932-152-CM26</t>
+          <t>1057417-15339-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4147,7 +4151,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4157,27 +4161,27 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.607.301-K</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Sociedad de Transporte Jiménez Hermanos Ltda.</t>
+          <t>TURISMO AYEKANTUN LIMITADA</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>76.036.979-9</t>
+          <t>76.470.279-4</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
@@ -4187,13 +4191,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>17149.02</v>
+        <v>42076.74</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>932-155-CM26</t>
+          <t>932-152-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4208,12 +4212,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -4233,12 +4237,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>CAR PLACE SPA</t>
+          <t>Sociedad de Transporte Jiménez Hermanos Ltda.</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>76.704.974-9</t>
+          <t>76.036.979-9</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -4248,13 +4252,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>35882.19</v>
+        <v>17149.02</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1197-107-CM26</t>
+          <t>932-155-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4269,7 +4273,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4289,17 +4293,17 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Felipe </t>
+          <t>CAR PLACE SPA</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>76.834.013-7</t>
+          <t>76.704.974-9</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4309,13 +4313,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>1452.68</v>
+        <v>35882.19</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1488-1234-CM26</t>
+          <t>1197-107-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4325,12 +4329,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>sep-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4340,27 +4344,27 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>61.602.232-6</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>TRANSERVI JL SPA</t>
+          <t xml:space="preserve">Felipe </t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>77.063.031-2</t>
+          <t>76.834.013-7</t>
         </is>
       </c>
       <c r="K63" t="inlineStr"/>
@@ -4370,13 +4374,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>46989.46</v>
+        <v>1452.68</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>299-168-CM26</t>
+          <t>1488-1234-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4391,37 +4395,37 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.602.232-6</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>CAR PLACE SPA</t>
+          <t>TRANSERVI JL SPA</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>76.704.974-9</t>
+          <t>77.063.031-2</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
@@ -4431,13 +4435,13 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>77200.13</v>
+        <v>46989.46</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1199-213-CM26</t>
+          <t>299-168-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4472,17 +4476,17 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>BUSES VILLAR</t>
+          <t>CAR PLACE SPA</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>76.465.610-5</t>
+          <t>76.704.974-9</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
@@ -4492,13 +4496,13 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>38554.16</v>
+        <v>77200.13</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>931-165-CM26</t>
+          <t>1199-213-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4513,12 +4517,12 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -4533,17 +4537,17 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>JOSUE MANUEL</t>
+          <t>BUSES VILLAR</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>76.370.023-2</t>
+          <t>76.465.610-5</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
@@ -4553,13 +4557,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>20647.27</v>
+        <v>38554.16</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>933-88-CM26</t>
+          <t>931-165-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4579,7 +4583,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -4594,17 +4598,17 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>TURISMO AYEKANTUN LIMITADA</t>
+          <t>JOSUE MANUEL</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>76.470.279-4</t>
+          <t>76.370.023-2</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
@@ -4614,13 +4618,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>3841.35</v>
+        <v>20647.27</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>933-70-CM26</t>
+          <t>933-88-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4635,12 +4639,12 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -4675,13 +4679,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>85024.07000000001</v>
+        <v>3841.35</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1059109-94-CM26</t>
+          <t>933-70-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4696,12 +4700,12 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -4716,17 +4720,17 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Julio Saavedra</t>
+          <t>TURISMO AYEKANTUN LIMITADA</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>76.248.427-7</t>
+          <t>76.470.279-4</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
@@ -4736,13 +4740,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>30258.13</v>
+        <v>85024.07000000001</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1197-123-CM26</t>
+          <t>1059109-94-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4762,7 +4766,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -4777,17 +4781,17 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Transporte Corporativo Infinity</t>
+          <t>Julio Saavedra</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>76.207.531-8</t>
+          <t>76.248.427-7</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
@@ -4797,13 +4801,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>6260.3</v>
+        <v>30258.13</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1197-122-CM26</t>
+          <t>1197-123-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4858,13 +4862,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>8555.75</v>
+        <v>6260.3</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2735-1056-CM26</t>
+          <t>1197-122-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4884,52 +4888,48 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>69.255.200-8</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD LO BARNECHEA</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+          <t>Transporte Corporativo Infinity</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>76.148.628-4</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.207.531-8</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>55142.84</v>
+        <v>8555.75</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>931-167-CM26</t>
+          <t>2735-1056-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4949,48 +4949,52 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>69.255.200-8</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>I MUNICIPALIDAD LO BARNECHEA</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>CAR PLACE SPA</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>76.704.974-9</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr"/>
+          <t>76.148.628-4</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>9912.15</v>
+        <v>55142.84</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>933-95-CM26</t>
+          <t>931-167-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5005,12 +5009,12 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -5025,37 +5029,33 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>CAR PLACE SPA</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.704.974-9</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>317.17</v>
+        <v>9912.15</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1057417-16197-CM26</t>
+          <t>933-95-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5070,7 +5070,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -5080,12 +5080,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>61.607.301-K</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5095,22 +5095,26 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>TURISMO AYEKANTUN LIMITADA</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>76.470.279-4</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr"/>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>22013.99</v>
+        <v>317.17</v>
       </c>
     </row>
     <row r="76">
@@ -5177,7 +5181,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2735-1197-CM26</t>
+          <t>1057417-16197-CM26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5202,27 +5206,27 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>69.255.200-8</t>
+          <t>61.607.301-K</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD LO BARNECHEA</t>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>AUTOMOTRIZ R Y R LIMITADA</t>
+          <t>TURISMO AYEKANTUN LIMITADA</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>77.951.690-3</t>
+          <t>76.470.279-4</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
@@ -5232,13 +5236,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>27536.25</v>
+        <v>22013.99</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1059109-101-CM26</t>
+          <t>2735-1197-CM26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5253,37 +5257,37 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>69.255.200-8</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>I MUNICIPALIDAD LO BARNECHEA</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Felipe </t>
+          <t>AUTOMOTRIZ R Y R LIMITADA</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>76.834.013-7</t>
+          <t>77.951.690-3</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
@@ -5293,13 +5297,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>926.26</v>
+        <v>27536.25</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2069-8569-CM26</t>
+          <t>1059109-101-CM26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5309,42 +5313,42 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>oct-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t xml:space="preserve">PESCO RENTAL SOCIEDAD ANONIMA </t>
+          <t xml:space="preserve">Felipe </t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>76.238.635-6</t>
+          <t>76.834.013-7</t>
         </is>
       </c>
       <c r="K79" t="inlineStr"/>
@@ -5354,13 +5358,13 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>590228.25</v>
+        <v>926.26</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>932-173-CM26</t>
+          <t>2069-8569-CM26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5375,7 +5379,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -5385,27 +5389,27 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Sociedad de Transporte Jiménez Hermanos Ltda.</t>
+          <t xml:space="preserve">PESCO RENTAL SOCIEDAD ANONIMA </t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>76.036.979-9</t>
+          <t>76.238.635-6</t>
         </is>
       </c>
       <c r="K80" t="inlineStr"/>
@@ -5415,13 +5419,13 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>1859.18</v>
+        <v>590228.25</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1200-241-CM26</t>
+          <t>932-173-CM26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5456,17 +5460,17 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>ALEXANDER SEBASTIÁN BERG KROLL</t>
+          <t>Sociedad de Transporte Jiménez Hermanos Ltda.</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>8.148.859-2</t>
+          <t>76.036.979-9</t>
         </is>
       </c>
       <c r="K81" t="inlineStr"/>
@@ -5476,13 +5480,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>35338.24</v>
+        <v>1859.18</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1059109-109-CM26</t>
+          <t>1200-241-CM26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5497,7 +5501,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -5517,17 +5521,17 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Julio Saavedra</t>
+          <t>ALEXANDER SEBASTIÁN BERG KROLL</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>76.248.427-7</t>
+          <t>8.148.859-2</t>
         </is>
       </c>
       <c r="K82" t="inlineStr"/>
@@ -5537,13 +5541,13 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>44861.8</v>
+        <v>35338.24</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1200-252-CM26</t>
+          <t>1059109-109-CM26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5578,37 +5582,33 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>ALEMOSO SPA</t>
+          <t>Julio Saavedra</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>77.852.175-K</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>Araucanía</t>
-        </is>
-      </c>
+          <t>76.248.427-7</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>8299.43</v>
+        <v>44861.8</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1523-2401-CM26</t>
+          <t>1200-252-CM26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5623,7 +5623,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5633,12 +5633,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>61.602.236-9</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL ARAUCANIA SUR HOSPITAL DR ABRAHAM GODOY PENA LAUTARO</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5648,28 +5648,32 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>ALEXANDRO DAVID GONZÁLEZ SALAZAR</t>
+          <t>ALEMOSO SPA</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>15.552.949-0</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr"/>
+          <t>77.852.175-K</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>7699.87</v>
+        <v>8299.43</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>1777-96-CM26</t>
+          <t>1523-2401-CM26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5694,27 +5698,27 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>60.804.012-9</t>
+          <t>61.602.236-9</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE ADUANAS</t>
+          <t>SERVICIO NACIONAL ARAUCANIA SUR HOSPITAL DR ABRAHAM GODOY PENA LAUTARO</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>David Isaac</t>
+          <t>ALEXANDRO DAVID GONZÁLEZ SALAZAR</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>76.820.816-6</t>
+          <t>15.552.949-0</t>
         </is>
       </c>
       <c r="K85" t="inlineStr"/>
@@ -5724,13 +5728,13 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>211983.43</v>
+        <v>7699.87</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>934-198-CM26</t>
+          <t>1777-96-CM26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5745,7 +5749,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5755,27 +5759,27 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>60.804.012-9</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>SERVICIO NACIONAL DE ADUANAS</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>CAR PLACE SPA</t>
+          <t>David Isaac</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>76.704.974-9</t>
+          <t>76.820.816-6</t>
         </is>
       </c>
       <c r="K86" t="inlineStr"/>
@@ -5785,71 +5789,132 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>3565.43</v>
+        <v>211983.43</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
+          <t>934-198-CM26</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>61.107.000-4</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>CAR PLACE SPA</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>76.704.974-9</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="n">
+        <v>3565.43</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
           <t>1057417-17061-SE26</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>2239-12-LR25</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
         <is>
           <t>oct-2026</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
+      <c r="D88" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
+      <c r="E88" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
+      <c r="F88" t="inlineStr">
         <is>
           <t>61.607.301-K</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
+      <c r="G88" t="inlineStr">
         <is>
           <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
+      <c r="H88" t="inlineStr">
         <is>
           <t>Biobío</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
+      <c r="I88" t="inlineStr">
         <is>
           <t>TRANSPORTES MONSALVE Y COMPAÑIA LIMITADA</t>
         </is>
       </c>
-      <c r="J87" t="inlineStr">
+      <c r="J88" t="inlineStr">
         <is>
           <t>76.701.245-4</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr">
+      <c r="K88" t="inlineStr">
         <is>
           <t>Araucanía</t>
         </is>
       </c>
-      <c r="L87" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="n">
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="n">
         <v>314520.87</v>
       </c>
     </row>
